--- a/samples/报价单模板.xlsx
+++ b/samples/报价单模板.xlsx
@@ -4,15 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22110" windowHeight="12255"/>
+    <workbookView windowWidth="21120" windowHeight="14860" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="报单价" sheetId="1" r:id="rId1"/>
+    <sheet name="支付方式" sheetId="2" r:id="rId2"/>
+    <sheet name="开票信息" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$P$13</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">报单价!$A$1:$P$13</definedName>
   </definedNames>
   <calcPr calcId="191029" calcCompleted="0" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
   <si>
     <t>报价单</t>
   </si>
@@ -46,16 +46,13 @@
     <t>联系人：</t>
   </si>
   <si>
-    <t>收款方式：</t>
-  </si>
-  <si>
-    <t>现付  -</t>
-  </si>
-  <si>
-    <t>报价单号码：</t>
-  </si>
-  <si>
-    <t>客户地址：</t>
+    <t>报价有效期：</t>
+  </si>
+  <si>
+    <t>我方销售代表：</t>
+  </si>
+  <si>
+    <t>送货地址：</t>
   </si>
   <si>
     <t>电话号码：</t>
@@ -67,18 +64,6 @@
     <t>增值税-专用发票</t>
   </si>
   <si>
-    <t>我方销售代表：</t>
-  </si>
-  <si>
-    <t>送货地址：</t>
-  </si>
-  <si>
-    <t>传真号码：</t>
-  </si>
-  <si>
-    <t>报价有效期：</t>
-  </si>
-  <si>
     <t>销售代表手机：</t>
   </si>
   <si>
@@ -131,6 +116,57 @@
   </si>
   <si>
     <t>含税合计</t>
+  </si>
+  <si>
+    <t>付款方式</t>
+  </si>
+  <si>
+    <t>支付比例</t>
+  </si>
+  <si>
+    <t>合同签订后一个月，甲方凭乙方开具的发票，向乙方支付合同总额的</t>
+  </si>
+  <si>
+    <t>项目验收通过一个月后，甲方凭项目验收单和乙方开具的发票向乙方支付合同总额的</t>
+  </si>
+  <si>
+    <t>合同到期后一个月内，甲方凭乙方开具的发示，向乙方支付合同总额的</t>
+  </si>
+  <si>
+    <t>客户名称</t>
+  </si>
+  <si>
+    <t>账号</t>
+  </si>
+  <si>
+    <t>税务登记号</t>
+  </si>
+  <si>
+    <t>开票地址电话</t>
+  </si>
+  <si>
+    <t>上海前卫实业有限公司</t>
+  </si>
+  <si>
+    <t>农行上海长兴支行03311510040003201</t>
+  </si>
+  <si>
+    <t>91310230133400024H</t>
+  </si>
+  <si>
+    <t>上海市长兴岛潘圆公路1999弄9号 021-3380 1858</t>
+  </si>
+  <si>
+    <t>上海城投长兴建设发展（集团）有限公司</t>
+  </si>
+  <si>
+    <t>农业银行上海市分行营业部03332200040033232</t>
+  </si>
+  <si>
+    <t>91310000676247951M</t>
+  </si>
+  <si>
+    <t>上海市崇明区长兴镇秋柑路688弄18号 021-33802222-8203</t>
   </si>
 </sst>
 </file>
@@ -143,8 +179,8 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
-    <numFmt numFmtId="177" formatCode="0_ "/>
-    <numFmt numFmtId="178" formatCode="0&quot;天&quot;"/>
+    <numFmt numFmtId="177" formatCode="0&quot;天&quot;"/>
+    <numFmt numFmtId="178" formatCode="0_ "/>
     <numFmt numFmtId="179" formatCode="00"/>
     <numFmt numFmtId="180" formatCode="&quot;￥&quot;#,##0.00_);[Red]\(&quot;￥&quot;#,##0.00\)"/>
     <numFmt numFmtId="181" formatCode="_ \¥* #,##0.00_ ;_ \¥* \-#,##0.00_ ;_ \¥* &quot;-&quot;??_ ;_ @_ "/>
@@ -369,7 +405,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -379,12 +415,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.05"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -727,7 +757,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -751,16 +781,16 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -769,91 +799,94 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -905,66 +938,70 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -976,7 +1013,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1000,7 +1037,7 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="181" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1015,9 +1052,6 @@
     <xf numFmtId="180" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1027,10 +1061,10 @@
     <xf numFmtId="180" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
@@ -1386,10 +1420,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:W18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="1" width="4.625" customWidth="1"/>
-    <col min="2" max="2" width="15.4166666666667" customWidth="1"/>
+    <col min="2" max="2" width="15.4196428571429" customWidth="1"/>
     <col min="3" max="3" width="12.5" customWidth="1"/>
     <col min="4" max="4" width="23.75" customWidth="1"/>
     <col min="5" max="5" width="12.375" customWidth="1"/>
@@ -1406,409 +1440,394 @@
     <col min="16" max="16" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" spans="1:23">
-      <c r="A1" s="5"/>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="20.25" spans="1:23">
-      <c r="A2" s="7" t="s">
+    <row r="1" ht="23.2" spans="1:23">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="23.2" spans="1:23">
+      <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
-      <c r="V2" s="8"/>
-      <c r="W2" s="8"/>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="21" customHeight="1" spans="1:23">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="10"/>
-      <c r="K3" s="11" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+    </row>
+    <row r="3" s="3" customFormat="1" ht="21" customHeight="1" spans="1:23">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="11"/>
+      <c r="K3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="12"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="11.25" spans="1:23">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="13"/>
-      <c r="U4" s="13"/>
-      <c r="V4" s="13"/>
-      <c r="W4" s="13"/>
-    </row>
-    <row r="5" s="2" customFormat="1" ht="11.25" spans="1:23">
-      <c r="A5" s="14" t="s">
+      <c r="L3" s="13"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+    </row>
+    <row r="4" s="3" customFormat="1" ht="13.6" spans="1:23">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="14"/>
+      <c r="W4" s="14"/>
+    </row>
+    <row r="5" s="3" customFormat="1" ht="13.6" spans="1:23">
+      <c r="A5" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="18" t="s">
+      <c r="B5" s="15"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="18" t="s">
+      <c r="F5" s="20"/>
+      <c r="G5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="20" t="s">
+      <c r="H5" s="21">
+        <v>14</v>
+      </c>
+      <c r="I5" s="22"/>
+      <c r="J5" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="21"/>
-      <c r="J5" s="18" t="s">
+      <c r="K5" s="23"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+    </row>
+    <row r="6" s="3" customFormat="1" ht="13.6" spans="1:23">
+      <c r="A6" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="22"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-    </row>
-    <row r="6" s="2" customFormat="1" ht="11.25" spans="1:23">
-      <c r="A6" s="14" t="s">
+      <c r="B6" s="15"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="18" t="s">
+      <c r="F6" s="25"/>
+      <c r="G6" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="23"/>
-      <c r="G6" s="18" t="s">
+      <c r="H6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="I6" s="23"/>
+      <c r="J6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="19"/>
-      <c r="J6" s="18" t="s">
+      <c r="K6" s="23"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+    </row>
+    <row r="7" s="3" customFormat="1" ht="13.6" spans="1:23">
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="28"/>
+      <c r="I7" s="23"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
+    </row>
+    <row r="8" s="3" customFormat="1" ht="13.6" spans="1:23">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14"/>
+    </row>
+    <row r="9" s="4" customFormat="1" ht="25" customHeight="1" spans="1:23">
+      <c r="A9" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="K6" s="22"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-    </row>
-    <row r="7" s="2" customFormat="1" ht="11.25" spans="1:23">
-      <c r="A7" s="14" t="s">
+      <c r="B9" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="18" t="s">
+      <c r="C9" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="18" t="s">
+      <c r="D9" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="25">
-        <v>14</v>
-      </c>
-      <c r="I7" s="19"/>
-      <c r="J7" s="26" t="s">
+      <c r="E9" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="K7" s="27"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
-    </row>
-    <row r="8" s="2" customFormat="1" ht="11.25" spans="1:23">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="18"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="13"/>
-      <c r="U8" s="13"/>
-      <c r="V8" s="13"/>
-      <c r="W8" s="13"/>
-    </row>
-    <row r="9" s="3" customFormat="1" ht="25" customHeight="1" spans="1:23">
-      <c r="A9" s="29" t="s">
+      <c r="F9" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="G9" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="H9" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="30" t="s">
+      <c r="I9" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="30" t="s">
+      <c r="J9" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="30" t="s">
+      <c r="K9" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="30" t="s">
+      <c r="L9" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="30" t="s">
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="33"/>
+      <c r="P9" s="33"/>
+      <c r="Q9" s="33"/>
+      <c r="R9" s="33"/>
+      <c r="S9" s="33"/>
+    </row>
+    <row r="10" s="5" customFormat="1" ht="39" customHeight="1" spans="1:23">
+      <c r="A10" s="34">
+        <v>1</v>
+      </c>
+      <c r="B10" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="K9" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="31"/>
-      <c r="S9" s="31"/>
-    </row>
-    <row r="10" s="4" customFormat="1" ht="39" customHeight="1" spans="1:23">
-      <c r="A10" s="32">
-        <v>1</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="38">
+      <c r="C10" s="35"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="40">
         <f>G10/(1+I10)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="J10" s="40">
+      <c r="I10" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="42">
         <f>H10*E10</f>
         <v>0</v>
       </c>
-      <c r="K10" s="40">
+      <c r="K10" s="42">
         <f>J10*I10</f>
         <v>0</v>
       </c>
-      <c r="L10" s="41">
+      <c r="L10" s="43">
         <f>H10*E10*(1+I10)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="42"/>
-      <c r="N10" s="42"/>
-      <c r="O10" s="42"/>
-      <c r="P10" s="42"/>
-      <c r="Q10" s="42"/>
-      <c r="R10" s="42"/>
-      <c r="S10" s="42"/>
-    </row>
-    <row r="11" s="4" customFormat="1" ht="50" customHeight="1" spans="1:23">
-      <c r="A11" s="32">
+      <c r="M10" s="44"/>
+      <c r="N10" s="44"/>
+      <c r="O10" s="44"/>
+      <c r="P10" s="44"/>
+      <c r="Q10" s="44"/>
+      <c r="R10" s="44"/>
+      <c r="S10" s="44"/>
+    </row>
+    <row r="11" s="5" customFormat="1" ht="50" customHeight="1" spans="1:23">
+      <c r="A11" s="34">
         <v>2</v>
       </c>
-      <c r="B11" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="33"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="38">
+      <c r="B11" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="35"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="40">
         <f>G11/(1+I11)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="45">
         <v>0.13</v>
       </c>
-      <c r="J11" s="40">
+      <c r="J11" s="42">
         <f>H11*E11</f>
         <v>0</v>
       </c>
-      <c r="K11" s="40">
+      <c r="K11" s="42">
         <f>J11*I11</f>
         <v>0</v>
       </c>
-      <c r="L11" s="41">
+      <c r="L11" s="43">
         <f>H11*E11*(1+I11)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="42"/>
-      <c r="N11" s="42"/>
-      <c r="O11" s="42"/>
-      <c r="P11" s="42"/>
-      <c r="Q11" s="42"/>
-      <c r="R11" s="42"/>
-      <c r="S11" s="42"/>
-    </row>
-    <row r="12" s="4" customFormat="1" ht="24" customHeight="1" spans="1:23">
-      <c r="A12" s="32">
+      <c r="M11" s="44"/>
+      <c r="N11" s="44"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
+    </row>
+    <row r="12" s="5" customFormat="1" ht="24" customHeight="1" spans="1:23">
+      <c r="A12" s="34">
         <v>3</v>
       </c>
-      <c r="B12" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="38">
+      <c r="B12" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="40">
         <f>G12/(1+I12)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="45">
         <v>0.06</v>
       </c>
-      <c r="J12" s="40">
+      <c r="J12" s="42">
         <f>H12*E12</f>
         <v>0</v>
       </c>
-      <c r="K12" s="40">
+      <c r="K12" s="42">
         <f>J12*I12</f>
         <v>0</v>
       </c>
-      <c r="L12" s="41">
+      <c r="L12" s="43">
         <f>H12*E12*(1+I12)</f>
         <v>0</v>
       </c>
-      <c r="M12" s="42"/>
-      <c r="N12" s="42"/>
-      <c r="O12" s="42"/>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="42"/>
-      <c r="S12" s="42"/>
+      <c r="M12" s="44"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="44"/>
+      <c r="S12" s="44"/>
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:23">
-      <c r="A13" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="44"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="45">
+      <c r="A13" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46">
         <f>SUM(J10:J12)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="45"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="J13" s="48">
+      <c r="E13" s="46"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="49">
         <f>L13-D13</f>
         <v>0</v>
       </c>
-      <c r="K13" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="L13" s="50">
+      <c r="K13" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="L13" s="51">
         <f>SUM(L10:L12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="7:7">
-      <c r="G18" s="51"/>
+      <c r="G18" s="52"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" selectLockedCells="1" insertRows="0" deleteRows="0" objects="1"/>
-  <mergeCells count="10">
+  <sheetProtection selectLockedCells="1" insertRows="0" deleteRows="0"/>
+  <mergeCells count="9">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A3:H3"/>
@@ -1816,16 +1835,16 @@
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="A13:C13"/>
   </mergeCells>
-  <dataValidations count="11">
+  <dataValidations count="10">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="项目名称" sqref="A1:L1"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="报价单位名称" sqref="A3:H3"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="报价日期" sqref="L3"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5">
-      <formula1>"现付  -,月结  -,季结  -,未定  -"</formula1>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="有效期大于1天小于30天" sqref="H5">
+      <formula1>1</formula1>
+      <formula2>30</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5">
       <formula1>"现金,支票,银行划帐"</formula1>
@@ -1833,21 +1852,17 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6">
       <formula1>"增值税-普通发票,增值税-专用发票"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="有效期大于1天小于30天" sqref="H7">
-      <formula1>1</formula1>
-      <formula2>30</formula2>
-    </dataValidation>
     <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L7">
       <formula1>11</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10 B11:B12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10:B12">
       <formula1>"软硬件商号,安装调试服务"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I10 I11:I12">
-      <formula1>"13%,6%"</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F7">
       <formula1>8</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I10:I12">
+      <formula1>"13%,6%"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.432638888888889" right="0.236111111111111" top="0.590277777777778" bottom="0.354166666666667" header="0.314583333333333" footer="0.196527777777778"/>
@@ -1855,8 +1870,8 @@
   <headerFooter alignWithMargins="0"/>
   <ignoredErrors>
     <ignoredError sqref="H10:I10" numberStoredAsText="1" unlockedFormula="1"/>
-    <ignoredError sqref="D13 J10:L10 H11:L12" unlockedFormula="1"/>
     <ignoredError sqref="B10:B11" listDataValidation="1"/>
+    <ignoredError sqref="H11:L12 D13 J10:L10" unlockedFormula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1864,9 +1879,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <sheetData/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" outlineLevelRow="3" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="89.1428571428571" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="1"/>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
@@ -1875,27 +1918,59 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <sheetData/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" outlineLevelRow="2" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="43.6428571428571" customWidth="1"/>
+    <col min="2" max="2" width="48.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="12.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="48.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<allowEditUser xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" hasInvisiblePropRange="0">
-  <rangeList sheetStid="1" master="" otherUserPermission="visible"/>
-  <rangeList sheetStid="2" master="" otherUserPermission="visible"/>
-  <rangeList sheetStid="3" master="" otherUserPermission="visible"/>
-</allowEditUser>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A5607D9-04D2-4DE1-AC0E-A7772F01BC71}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>